--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-10-2025.xlsx
@@ -591,27 +591,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -712,27 +712,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -833,27 +833,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -954,27 +954,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1075,27 +1075,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1196,27 +1196,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1317,27 +1317,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: Exceeded 30 redirects.</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1438,27 +1438,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1559,27 +1559,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1680,27 +1680,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1801,27 +1801,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -1922,27 +1922,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2043,27 +2043,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2164,27 +2164,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2285,27 +2285,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2503,27 +2503,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2624,27 +2624,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2745,27 +2745,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2866,27 +2866,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -2987,27 +2987,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -3108,27 +3108,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -3229,27 +3229,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -3350,27 +3350,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
@@ -3471,27 +3471,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6643be8e5+80021]
-	GetHandleVerifier [0x0x7ff6643be940+80112]
-	(No symbol) [0x0x7ff66414060f]
-	(No symbol) [0x0x7ff664198854]
-	(No symbol) [0x0x7ff664198b1c]
-	(No symbol) [0x0x7ff6641ec927]
-	(No symbol) [0x0x7ff6641c126f]
-	(No symbol) [0x0x7ff6641e968a]
-	(No symbol) [0x0x7ff6641c1003]
-	(No symbol) [0x0x7ff6641895d1]
-	(No symbol) [0x0x7ff66418a3f3]
-	GetHandleVerifier [0x0x7ff66467dc7d+2960429]
-	GetHandleVerifier [0x0x7ff664677f3a+2936554]
-	GetHandleVerifier [0x0x7ff664698977+3070247]
-	GetHandleVerifier [0x0x7ff6643d83ce+185214]
-	GetHandleVerifier [0x0x7ff6643dfe1f+216527]
-	GetHandleVerifier [0x0x7ff6643c7b24+117460]
-	GetHandleVerifier [0x0x7ff6643c7cdf+117903]
-	GetHandleVerifier [0x0x7ff6643adbb8+11112]
-	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
-	RtlUserThreadStart [0x0x7ffe9552c53c+44]
+	GetHandleVerifier [0x0x7ff7ccfbe8e5+80021]
+	GetHandleVerifier [0x0x7ff7ccfbe940+80112]
+	(No symbol) [0x0x7ff7ccd4060f]
+	(No symbol) [0x0x7ff7ccd98854]
+	(No symbol) [0x0x7ff7ccd98b1c]
+	(No symbol) [0x0x7ff7ccdec927]
+	(No symbol) [0x0x7ff7ccdc126f]
+	(No symbol) [0x0x7ff7ccde968a]
+	(No symbol) [0x0x7ff7ccdc1003]
+	(No symbol) [0x0x7ff7ccd895d1]
+	(No symbol) [0x0x7ff7ccd8a3f3]
+	GetHandleVerifier [0x0x7ff7cd27dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7cd277f3a+2936554]
+	GetHandleVerifier [0x0x7ff7cd298977+3070247]
+	GetHandleVerifier [0x0x7ff7ccfd83ce+185214]
+	GetHandleVerifier [0x0x7ff7ccfdfe1f+216527]
+	GetHandleVerifier [0x0x7ff7ccfc7b24+117460]
+	GetHandleVerifier [0x0x7ff7ccfc7cdf+117903]
+	GetHandleVerifier [0x0x7ff7ccfadbb8+11112]
+	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
+	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
         </is>
       </c>
